--- a/output/pdf_financials_xlsx/NICU.xlsx
+++ b/output/pdf_financials_xlsx/NICU.xlsx
@@ -1192,13 +1192,13 @@
         <v>-0.074671</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>6.762966</v>
+        <v>-6.762966</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>21.96958</v>
+        <v>-21.96958</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>9.721878999999999</v>
+        <v>-9.721878999999999</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>-16.268</v>
@@ -1448,13 +1448,13 @@
         <v>-0.074671</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>6.762966</v>
+        <v>-6.762966</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>21.96958</v>
+        <v>-21.96958</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>9.721878999999999</v>
+        <v>-9.721878999999999</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>-16.268</v>
@@ -1601,13 +1601,13 @@
         <v>-0.074671</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>6.762966</v>
+        <v>-6.762966</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>21.96958</v>
+        <v>-21.96958</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>9.721878999999999</v>
+        <v>-9.721878999999999</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>-16.268</v>
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>83.534525</v>
+        <v>-83.534525</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>162.031317</v>
+        <v>-162.031317</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>162.68</v>
@@ -1817,13 +1817,13 @@
         <v>-0.074671</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>6.762966</v>
+        <v>-6.762966</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>21.96958</v>
+        <v>-21.96958</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>9.721878999999999</v>
+        <v>-9.721878999999999</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-16.268</v>
@@ -1877,10 +1877,10 @@
         <v>0.062081</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.08309900000000001</v>
+        <v>0.083</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>7.385</v>
       </c>
     </row>
     <row r="29">
@@ -1919,19 +1919,19 @@
         <v>-0.074671</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>6.762966</v>
+        <v>-6.762966</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>22.002023</v>
+        <v>-21.937137</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>9.78396</v>
+        <v>-9.659798</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-16.184901</v>
+        <v>-16.185</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-16.983</v>
+        <v>-9.598000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-28.86596185878913</v>
+        <v>-16.31369616208315</v>
       </c>
     </row>
     <row r="31">
@@ -2045,13 +2045,13 @@
         <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>-0</v>
@@ -5144,37 +5144,37 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.105428</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.105428</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.079183</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.079183</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.079183</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.079183</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.100713</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.100713</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.492221</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.158931</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.158931</v>
       </c>
       <c r="N92" s="3" t="n">
         <v>5.374</v>
@@ -5553,10 +5553,10 @@
         <v>0</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>11.536</v>
       </c>
     </row>
     <row r="101">
@@ -12230,7 +12230,11 @@
           <t>Share-based payment reserve 18,20 3,945,452</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -12314,7 +12318,11 @@
           <t>Warrants reserve 19 1,429,209</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -13866,7 +13874,11 @@
           <t>Share-based payment reserve 17, 19</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -13950,7 +13962,11 @@
           <t>Warrants reserve 18</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -15066,7 +15082,11 @@
           <t>Share-based payment reserve 16, 18</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -15150,7 +15170,11 @@
           <t>Warrants reserve 17</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -15746,7 +15770,11 @@
           <t>Share-based payments reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -16148,7 +16176,11 @@
           <t>Share-based payments reserve (Note 4)</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -16480,7 +16512,11 @@
           <t>Share-based payments reserve (Note 3)</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -17776,7 +17812,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -29000,7 +29036,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -32310,13 +32346,13 @@
         </is>
       </c>
       <c r="O290" s="5" t="n">
-        <v>21.96958</v>
+        <v>-21.96958</v>
       </c>
       <c r="P290" s="5" t="n">
-        <v>9.721878999999999</v>
+        <v>-9.721878999999999</v>
       </c>
       <c r="Q290" s="5" t="n">
-        <v>16.267727</v>
+        <v>-16.267727</v>
       </c>
       <c r="R290" t="inlineStr">
         <is>
@@ -34705,10 +34741,10 @@
         </is>
       </c>
       <c r="N318" s="5" t="n">
-        <v>6.762966</v>
+        <v>-6.762966</v>
       </c>
       <c r="O318" s="5" t="n">
-        <v>21.96958</v>
+        <v>-21.96958</v>
       </c>
       <c r="P318" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/NICU.xlsx
+++ b/output/pdf_financials_xlsx/NICU.xlsx
@@ -988,16 +988,16 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.001811</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.09698900000000001</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.856599</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.401247</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>0</v>
@@ -1817,16 +1817,16 @@
         <v>-0.074671</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-6.762966</v>
+        <v>-6.764777</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-21.96958</v>
+        <v>-22.066569</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-9.721878999999999</v>
+        <v>-10.578478</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-16.268</v>
+        <v>-16.669247</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>-16.983</v>
@@ -1919,16 +1919,16 @@
         <v>-0.074671</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-6.762966</v>
+        <v>-6.764777</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-21.937137</v>
+        <v>-22.034126</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-9.659798</v>
+        <v>-10.516397</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-16.185</v>
+        <v>-16.586247</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-9.598000000000001</v>
@@ -2149,40 +2149,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.111255</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.62399</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.504053</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.020553</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.152061</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.064221</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.018026</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.07323499999999999</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.002366</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>5.682332</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>6.175126</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>6.175126</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>17.535</v>
@@ -2247,40 +2247,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.111255</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.62399</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.504053</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.020553</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.152061</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.064221</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.018026</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.07323499999999999</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.002366</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>5.682332</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>6.175126</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>6.175126</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>17.535</v>
@@ -2835,25 +2835,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.111255</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.62399</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.504053</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.020553</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.152061</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.064221</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.018026</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
@@ -2862,13 +2862,13 @@
         <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>5.727854</v>
+        <v>0.045522</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>6.283073</v>
+        <v>0.107947</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>6.283073</v>
+        <v>0.107947</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.411</v>
@@ -10216,7 +10216,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -15520,7 +15520,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -16012,7 +16012,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -16266,7 +16266,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -17028,7 +17028,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
@@ -31774,7 +31774,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -32032,7 +32032,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -33232,7 +33232,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -34344,7 +34344,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -34432,7 +34432,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">

--- a/output/pdf_financials_xlsx/NICU.xlsx
+++ b/output/pdf_financials_xlsx/NICU.xlsx
@@ -1868,10 +1868,10 @@
         <v>0</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.011568</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.032443</v>
+        <v>0.019831</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>0.062081</v>
@@ -1919,10 +1919,10 @@
         <v>-0.074671</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-6.764777</v>
+        <v>-6.753209</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-22.034126</v>
+        <v>-22.046738</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-10.516397</v>
@@ -5544,10 +5544,10 @@
         <v>0</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.011568</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.019831</v>
       </c>
       <c r="M100" s="3" t="n">
         <v>0</v>
@@ -24474,7 +24474,11 @@
           <t>Depreciation of right of use assets</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NICU.xlsx
+++ b/output/pdf_financials_xlsx/NICU.xlsx
@@ -599,10 +599,8 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -703,10 +701,8 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>9.1e-05</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0.000203</v>
@@ -754,10 +750,8 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
@@ -805,10 +799,8 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0</v>
@@ -856,10 +848,8 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>9.1e-05</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.000203</v>
@@ -958,10 +948,8 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -1009,10 +997,8 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>-0</v>
@@ -1060,10 +1046,8 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>0</v>
@@ -1111,10 +1095,8 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>0</v>
@@ -1162,10 +1144,8 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.002069</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.116841</v>
@@ -1213,10 +1193,8 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
@@ -1418,10 +1396,8 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.002069</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.116841</v>
@@ -1469,10 +1445,8 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -1520,10 +1494,8 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>0</v>
@@ -1571,10 +1543,8 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-0.002069</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.116841</v>
@@ -1622,10 +1592,8 @@
           <t>EPS (Basic)</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="3" t="n">
+        <v>-0.01</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>-0.03</v>
@@ -1675,10 +1643,8 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>-0.01</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>-0.03</v>
@@ -1787,10 +1753,8 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.002069</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.116841</v>
@@ -1838,10 +1802,8 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0</v>
@@ -1889,10 +1851,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.002069</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.116841</v>
@@ -2015,10 +1975,8 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -3861,19 +3819,19 @@
         <v>0.038422</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.52362</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.672579</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.786983</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>2.349</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="68">
@@ -5463,10 +5421,8 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.002069</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-0.116841</v>
@@ -5514,10 +5470,8 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>0</v>
@@ -5565,10 +5519,8 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>-0.00065</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>-0.014827</v>
@@ -5616,10 +5568,8 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C102" s="3" t="n">
         <v>0</v>
@@ -5667,10 +5617,8 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C103" s="3" t="n">
         <v>0</v>
@@ -5718,10 +5666,8 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.002774</v>
       </c>
       <c r="C104" s="3" t="n">
         <v>-0.003215</v>
@@ -5769,10 +5715,8 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C105" s="3" t="n">
         <v>0</v>
@@ -5820,10 +5764,8 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.002124</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>-0.057028</v>
@@ -5871,10 +5813,8 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>0.07785499999999999</v>
@@ -5922,10 +5862,8 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C108" s="3" t="n">
         <v>0</v>
@@ -5973,10 +5911,8 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C109" s="3" t="n">
         <v>0</v>
@@ -6024,10 +5960,8 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -6075,10 +6009,8 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -6105,16 +6037,16 @@
         <v>0</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.016115</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.056227</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.034304</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.024371</v>
       </c>
       <c r="O111" s="3" t="n">
         <v>0</v>
@@ -6126,10 +6058,8 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -6177,10 +6107,8 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C113" s="3" t="n">
         <v>0</v>
@@ -6228,10 +6156,8 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -6279,10 +6205,8 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -6330,10 +6254,8 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
         <v>0</v>
@@ -6381,10 +6303,8 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C117" s="3" t="n">
         <v>0</v>
@@ -6432,10 +6352,8 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>0</v>
@@ -6550,10 +6468,8 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -6601,10 +6517,8 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -6652,10 +6566,8 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C122" s="3" t="n">
         <v>0</v>
@@ -6703,10 +6615,8 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>0</v>
@@ -6754,10 +6664,8 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -6805,10 +6713,8 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -6856,10 +6762,8 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C126" s="3" t="n">
         <v>0</v>
@@ -6984,10 +6888,8 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C128" s="3" t="n">
         <v>0</v>
@@ -7098,10 +7000,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0.111255</v>
       </c>
       <c r="C130" s="3" t="n">
         <v>0.111255</v>
@@ -7149,10 +7049,8 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C131" s="3" t="n">
         <v>0</v>
@@ -7200,10 +7098,8 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C132" s="3" t="n">
         <v>0.5127350000000001</v>
@@ -7251,10 +7147,8 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.111255</v>
       </c>
       <c r="C133" s="3" t="n">
         <v>0.62399</v>
@@ -7302,10 +7196,8 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -7332,16 +7224,16 @@
         <v>0</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.016115</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.056227</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.034304</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.024371</v>
       </c>
       <c r="O134" s="3" t="n">
         <v>0</v>
@@ -7399,16 +7291,16 @@
         </is>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-5.768362</v>
+        <v>-5.784477</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-18.167799</v>
+        <v>-18.224026</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-10.535734</v>
+        <v>-10.570038</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-17.81</v>
+        <v>-17.834371</v>
       </c>
       <c r="O135" s="3" t="n">
         <v>-35.098</v>
@@ -7425,7 +7317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R358"/>
+  <dimension ref="A1:R374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -22066,7 +21958,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -28853,29 +28749,29 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>CASH FLOWS FROM (USED IN) OPERATING ACTIVITIES</t>
+        </is>
+      </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Revenue 7 $</t>
+          <t>Net income (loss) for the period $</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E250" s="5" t="n">
+        <v>-0.002069</v>
+      </c>
+      <c r="F250" s="5" t="n">
+        <v>-0.116841</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
@@ -28932,36 +28828,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R250" s="5" t="n">
-        <v>58.834</v>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
+          <t>Share-based payments                                           77,855              −</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Mine operating costs 8</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr"/>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Increase in amounts receivable</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E251" s="5" t="n">
+        <v>-0.00065</v>
+      </c>
+      <c r="F251" s="5" t="n">
+        <v>-0.014827</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
@@ -29018,40 +28916,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R251" s="5" t="n">
-        <v>53.53</v>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
+          <t>Share-based payments                                           77,855              −</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Depletion, depreciation and amortization 8,9</t>
+          <t>Decrease in amounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E252" s="5" t="n">
+        <v>0.002774</v>
+      </c>
+      <c r="F252" s="5" t="n">
+        <v>-0.003215</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
@@ -29108,40 +29004,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R252" s="5" t="n">
-        <v>7.385</v>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
+          <t>Share-based payments                                           77,855              −</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share-based payments                                           77,855              − total</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" s="5" t="n">
+        <v>5.5e-05</v>
+      </c>
+      <c r="F253" s="5" t="n">
+        <v>-0.057028</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
@@ -29198,36 +29088,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R253" s="5" t="n">
-        <v>60.915</v>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
+          <t>CASH FLOWS FROM (USED IN) INVESTING ACTIVITY</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Loss from mining operations</t>
+          <t>Financing costs paid</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E254" s="5" t="n">
+        <v>-0.0288</v>
+      </c>
+      <c r="F254" s="5" t="n">
+        <v>-0.007274</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
@@ -29284,36 +29172,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R254" s="5" t="n">
-        <v>-2.081</v>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Corporate and general</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Issue of common shares</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E255" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F255" s="5" t="n">
+        <v>0.7255</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
@@ -29365,39 +29255,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q255" s="5" t="n">
-        <v>7.258</v>
-      </c>
-      <c r="R255" s="5" t="n">
-        <v>8.359999999999999</v>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
+          <t>Share issue costs paid                                                (148,463)             −</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Share-based compensation 24,26</t>
+          <t>Share issue costs paid                                                (148,463)             − total</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E256" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F256" s="5" t="n">
+        <v>0.577037</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
@@ -29449,39 +29339,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q256" s="5" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R256" s="5" t="n">
-        <v>4.065</v>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
+          <t>Share issue costs paid                                                (148,463)             −</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Exploration and evaluation</t>
+          <t>INCREASE IN CASH DURING THE PERIOD</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E257" s="5" t="n">
+        <v>0.111255</v>
+      </c>
+      <c r="F257" s="5" t="n">
+        <v>0.5127350000000001</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
@@ -29533,39 +29423,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q257" s="5" t="n">
-        <v>10.117</v>
-      </c>
-      <c r="R257" s="5" t="n">
-        <v>8.226000000000001</v>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
+          <t>CASH, beginning of period                                            111,255              −</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Site maintenance</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr"/>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CASH, end of period $</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E258" s="5" t="n">
+        <v>0.111255</v>
+      </c>
+      <c r="F258" s="5" t="n">
+        <v>0.62399</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
@@ -29617,11 +29511,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q258" s="5" t="n">
-        <v>0.246</v>
-      </c>
-      <c r="R258" s="5" t="n">
-        <v>10.488</v>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="259">
@@ -29630,19 +29528,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Cost of sales</t>
-        </is>
-      </c>
+      <c r="B259" t="inlineStr"/>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Operating loss</t>
+          <t>Revenue 7 $</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -29705,11 +29599,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q259" s="5" t="n">
-        <v>-19.461</v>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R259" s="5" t="n">
-        <v>-33.22</v>
+        <v>58.834</v>
       </c>
     </row>
     <row r="260">
@@ -29725,7 +29621,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Flow-through premium income</t>
+          <t>Mine operating costs 8</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
@@ -29789,13 +29685,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q260" s="5" t="n">
-        <v>2.945</v>
-      </c>
-      <c r="R260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R260" s="5" t="n">
+        <v>53.53</v>
       </c>
     </row>
     <row r="261">
@@ -29811,10 +29707,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Finance and interest expense 10(a)</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr"/>
+          <t>Depletion, depreciation and amortization 8,9</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -29875,11 +29775,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q261" s="5" t="n">
-        <v>-0.173</v>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R261" s="5" t="n">
-        <v>-4.938</v>
+        <v>7.385</v>
       </c>
     </row>
     <row r="262">
@@ -29895,10 +29797,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Gain on bargain purchase of KGHM assets 5</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr"/>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -29965,7 +29871,7 @@
         </is>
       </c>
       <c r="R262" s="5" t="n">
-        <v>19.513</v>
+        <v>60.915</v>
       </c>
     </row>
     <row r="263">
@@ -29981,7 +29887,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Costs on purchase of KGHM assets 5</t>
+          <t>Loss from mining operations</t>
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
@@ -30051,7 +29957,7 @@
         </is>
       </c>
       <c r="R263" s="5" t="n">
-        <v>-2.491</v>
+        <v>-2.081</v>
       </c>
     </row>
     <row r="264">
@@ -30067,7 +29973,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Accretion of streaming liability 18</t>
+          <t>Corporate and general</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -30131,13 +30037,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q264" s="5" t="n">
+        <v>7.258</v>
       </c>
       <c r="R264" s="5" t="n">
-        <v>-2.47</v>
+        <v>8.359999999999999</v>
       </c>
     </row>
     <row r="265">
@@ -30153,7 +30057,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Accretion of asset retirement obligation 20</t>
+          <t>Share-based compensation 24,26</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -30218,10 +30122,10 @@
         </is>
       </c>
       <c r="Q265" s="5" t="n">
-        <v>-0.023</v>
+        <v>1.84</v>
       </c>
       <c r="R265" s="5" t="n">
-        <v>-0.389</v>
+        <v>4.065</v>
       </c>
     </row>
     <row r="266">
@@ -30237,7 +30141,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Gain on disposal of equipment</t>
+          <t>Exploration and evaluation</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -30302,12 +30206,10 @@
         </is>
       </c>
       <c r="Q266" s="5" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="R266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>10.117</v>
+      </c>
+      <c r="R266" s="5" t="n">
+        <v>8.226000000000001</v>
       </c>
     </row>
     <row r="267">
@@ -30323,7 +30225,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Other income 10(b)</t>
+          <t>Site maintenance</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -30388,10 +30290,10 @@
         </is>
       </c>
       <c r="Q267" s="5" t="n">
-        <v>0.439</v>
+        <v>0.246</v>
       </c>
       <c r="R267" s="5" t="n">
-        <v>1.124</v>
+        <v>10.488</v>
       </c>
     </row>
     <row r="268">
@@ -30407,10 +30309,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Loss before income and mining taxes</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr"/>
+          <t>Operating loss</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -30472,10 +30378,10 @@
         </is>
       </c>
       <c r="Q268" s="5" t="n">
-        <v>-16.268</v>
+        <v>-19.461</v>
       </c>
       <c r="R268" s="5" t="n">
-        <v>-22.871</v>
+        <v>-33.22</v>
       </c>
     </row>
     <row r="269">
@@ -30486,12 +30392,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Income and mining tax recovery (expense)</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Current income expense 21</t>
+          <t>Flow-through premium income</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
@@ -30555,13 +30461,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R269" s="5" t="n">
-        <v>-0.01</v>
+      <c r="Q269" s="5" t="n">
+        <v>2.945</v>
+      </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="270">
@@ -30572,12 +30478,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Income and mining tax recovery (expense)</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Deferred income and mining tax recovery 21</t>
+          <t>Finance and interest expense 10(a)</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -30641,13 +30547,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q270" s="5" t="n">
+        <v>-0.173</v>
       </c>
       <c r="R270" s="5" t="n">
-        <v>5.898</v>
+        <v>-4.938</v>
       </c>
     </row>
     <row r="271">
@@ -30658,12 +30562,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Income and mining tax recovery (expense)</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Total income and mining tax recovery</t>
+          <t>Gain on bargain purchase of KGHM assets 5</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -30733,7 +30637,7 @@
         </is>
       </c>
       <c r="R271" s="5" t="n">
-        <v>5.888</v>
+        <v>19.513</v>
       </c>
     </row>
     <row r="272">
@@ -30744,19 +30648,15 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Income and mining tax recovery (expense)</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Costs on purchase of KGHM assets 5</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -30817,11 +30717,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q272" s="5" t="n">
-        <v>-16.268</v>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R272" s="5" t="n">
-        <v>-16.983</v>
+        <v>-2.491</v>
       </c>
     </row>
     <row r="273">
@@ -30832,19 +30734,15 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Income and mining tax recovery (expense)</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share 23 $</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Accretion of streaming liability 18</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -30905,11 +30803,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q273" s="5" t="n">
-        <v>-1e-07</v>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R273" s="5" t="n">
-        <v>-8e-08</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="274">
@@ -30920,12 +30820,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Weighted average number of outstanding shares</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Basic and diluted 23</t>
+          <t>Accretion of asset retirement obligation 20</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
@@ -30990,10 +30890,10 @@
         </is>
       </c>
       <c r="Q274" s="5" t="n">
-        <v>170766.096</v>
+        <v>-0.023</v>
       </c>
       <c r="R274" s="5" t="n">
-        <v>215042.407</v>
+        <v>-0.389</v>
       </c>
     </row>
     <row r="275">
@@ -31004,12 +30904,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Exploration and evaluation 11,21,22 $</t>
+          <t>Gain on disposal of equipment</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
@@ -31068,11 +30968,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P275" s="5" t="n">
-        <v>7.646763</v>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q275" s="5" t="n">
-        <v>10.116892</v>
+        <v>0.005</v>
       </c>
       <c r="R275" t="inlineStr">
         <is>
@@ -31088,19 +30990,15 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>General and administrative 21</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Other income 10(b)</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -31156,16 +31054,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P276" s="5" t="n">
-        <v>2.110059</v>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q276" s="5" t="n">
-        <v>5.038372</v>
-      </c>
-      <c r="R276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.439</v>
+      </c>
+      <c r="R276" s="5" t="n">
+        <v>1.124</v>
       </c>
     </row>
     <row r="277">
@@ -31176,12 +31074,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Share-based compensation 18,20</t>
+          <t>Loss before income and mining taxes</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
@@ -31240,16 +31138,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P277" s="5" t="n">
-        <v>1.458031</v>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q277" s="5" t="n">
-        <v>1.840375</v>
-      </c>
-      <c r="R277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-16.268</v>
+      </c>
+      <c r="R277" s="5" t="n">
+        <v>-22.871</v>
       </c>
     </row>
     <row r="278">
@@ -31260,19 +31158,15 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Income and mining tax recovery (expense)</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Current income expense 21</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
@@ -31318,22 +31212,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N278" s="5" t="n">
-        <v>0.155134</v>
-      </c>
-      <c r="O278" s="5" t="n">
-        <v>0.304368</v>
-      </c>
-      <c r="P278" s="5" t="n">
-        <v>0.634891</v>
-      </c>
-      <c r="Q278" s="5" t="n">
-        <v>1.958448</v>
-      </c>
-      <c r="R278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R278" s="5" t="n">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="279">
@@ -31344,12 +31244,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Income and mining tax recovery (expense)</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Property maintenance 21</t>
+          <t>Deferred income and mining tax recovery 21</t>
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
@@ -31408,16 +31308,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P279" s="5" t="n">
-        <v>0.504178</v>
-      </c>
-      <c r="Q279" s="5" t="n">
-        <v>0.161901</v>
-      </c>
-      <c r="R279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R279" s="5" t="n">
+        <v>5.898</v>
       </c>
     </row>
     <row r="280">
@@ -31428,19 +31330,15 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Income and mining tax recovery (expense)</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Marketing and promotion</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Total income and mining tax recovery</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -31486,22 +31384,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N280" s="5" t="n">
-        <v>0.133366</v>
-      </c>
-      <c r="O280" s="5" t="n">
-        <v>0.034996</v>
-      </c>
-      <c r="P280" s="5" t="n">
-        <v>0.175446</v>
-      </c>
-      <c r="Q280" s="5" t="n">
-        <v>0.261151</v>
-      </c>
-      <c r="R280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R280" s="5" t="n">
+        <v>5.888</v>
       </c>
     </row>
     <row r="281">
@@ -31512,17 +31416,17 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Income and mining tax recovery (expense)</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Depreciation 9</t>
+          <t>Net loss and comprehensive loss $</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -31580,16 +31484,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P281" s="5" t="n">
-        <v>0.062081</v>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q281" s="5" t="n">
-        <v>0.08309900000000001</v>
-      </c>
-      <c r="R281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-16.268</v>
+      </c>
+      <c r="R281" s="5" t="n">
+        <v>-16.983</v>
       </c>
     </row>
     <row r="282">
@@ -31600,17 +31504,17 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Income and mining tax recovery (expense)</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Total operating expenses</t>
+          <t>Basic and diluted loss per share 23 $</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -31658,22 +31562,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N282" s="5" t="n">
-        <v>6.83428</v>
-      </c>
-      <c r="O282" s="5" t="n">
-        <v>22.308405</v>
-      </c>
-      <c r="P282" s="5" t="n">
-        <v>12.591449</v>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q282" s="5" t="n">
-        <v>19.460238</v>
-      </c>
-      <c r="R282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-07</v>
+      </c>
+      <c r="R282" s="5" t="n">
+        <v>-8e-08</v>
       </c>
     </row>
     <row r="283">
@@ -31684,12 +31592,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Weighted average number of outstanding shares</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Flow-through premium income 16,27</t>
+          <t>Basic and diluted 23</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
@@ -31748,16 +31656,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P283" s="5" t="n">
-        <v>2.392425</v>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q283" s="5" t="n">
-        <v>2.944597</v>
-      </c>
-      <c r="R283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>170766.096</v>
+      </c>
+      <c r="R283" s="5" t="n">
+        <v>215042.407</v>
       </c>
     </row>
     <row r="284">
@@ -31768,19 +31676,15 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation 11,21,22 $</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -31831,14 +31735,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O284" s="5" t="n">
-        <v>0.09698900000000001</v>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P284" s="5" t="n">
-        <v>0.856599</v>
+        <v>7.646763</v>
       </c>
       <c r="Q284" s="5" t="n">
-        <v>0.401247</v>
+        <v>10.116892</v>
       </c>
       <c r="R284" t="inlineStr">
         <is>
@@ -31854,15 +31760,19 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Accretion of asset retirement obligation 13</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr"/>
+          <t>General and administrative 21</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -31919,10 +31829,10 @@
         </is>
       </c>
       <c r="P285" s="5" t="n">
-        <v>-0.026501</v>
+        <v>2.110059</v>
       </c>
       <c r="Q285" s="5" t="n">
-        <v>-0.02311</v>
+        <v>5.038372</v>
       </c>
       <c r="R285" t="inlineStr">
         <is>
@@ -31938,19 +31848,15 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Share-based compensation 18,20</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -32007,10 +31913,10 @@
         </is>
       </c>
       <c r="P286" s="5" t="n">
-        <v>0.004807</v>
+        <v>1.458031</v>
       </c>
       <c r="Q286" s="5" t="n">
-        <v>0.037405</v>
+        <v>1.840375</v>
       </c>
       <c r="R286" t="inlineStr">
         <is>
@@ -32026,17 +31932,17 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Interest expense 27</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -32084,21 +31990,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N287" s="5" t="n">
+        <v>0.155134</v>
+      </c>
+      <c r="O287" s="5" t="n">
+        <v>0.304368</v>
       </c>
       <c r="P287" s="5" t="n">
-        <v>-0.35776</v>
+        <v>0.634891</v>
       </c>
       <c r="Q287" s="5" t="n">
-        <v>-0.173124</v>
+        <v>1.958448</v>
       </c>
       <c r="R287" t="inlineStr">
         <is>
@@ -32114,12 +32016,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Gain on disposal of equipment</t>
+          <t>Property maintenance 21</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -32173,16 +32075,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O288" s="5" t="n">
-        <v>0.001504</v>
-      </c>
-      <c r="P288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P288" s="5" t="n">
+        <v>0.504178</v>
       </c>
       <c r="Q288" s="5" t="n">
-        <v>0.005496</v>
+        <v>0.161901</v>
       </c>
       <c r="R288" t="inlineStr">
         <is>
@@ -32198,17 +32100,17 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Total other income</t>
+          <t>Marketing and promotion</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -32256,21 +32158,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N289" s="5" t="n">
+        <v>0.133366</v>
+      </c>
+      <c r="O289" s="5" t="n">
+        <v>0.034996</v>
       </c>
       <c r="P289" s="5" t="n">
-        <v>2.86957</v>
+        <v>0.175446</v>
       </c>
       <c r="Q289" s="5" t="n">
-        <v>3.192511</v>
+        <v>0.261151</v>
       </c>
       <c r="R289" t="inlineStr">
         <is>
@@ -32286,17 +32184,17 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
+          <t>Depreciation 9</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -32349,14 +32247,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O290" s="5" t="n">
-        <v>-21.96958</v>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P290" s="5" t="n">
-        <v>-9.721878999999999</v>
+        <v>0.062081</v>
       </c>
       <c r="Q290" s="5" t="n">
-        <v>-16.267727</v>
+        <v>0.08309900000000001</v>
       </c>
       <c r="R290" t="inlineStr">
         <is>
@@ -32372,17 +32272,17 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share 17 $</t>
+          <t>Total operating expenses</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -32430,21 +32330,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N291" s="5" t="n">
+        <v>6.83428</v>
+      </c>
+      <c r="O291" s="5" t="n">
+        <v>22.308405</v>
       </c>
       <c r="P291" s="5" t="n">
-        <v>5.999999999999999e-08</v>
+        <v>12.591449</v>
       </c>
       <c r="Q291" s="5" t="n">
-        <v>1e-07</v>
+        <v>19.460238</v>
       </c>
       <c r="R291" t="inlineStr">
         <is>
@@ -32460,12 +32356,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>outstanding shares</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
+          <t>Flow-through premium income 16,27</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -32525,10 +32421,10 @@
         </is>
       </c>
       <c r="P292" s="5" t="n">
-        <v>160.9653</v>
+        <v>2.392425</v>
       </c>
       <c r="Q292" s="5" t="n">
-        <v>170.766096</v>
+        <v>2.944597</v>
       </c>
       <c r="R292" t="inlineStr">
         <is>
@@ -32544,15 +32440,19 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Exploration and evaluation 10, 20, 21 $</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -32604,15 +32504,13 @@
         </is>
       </c>
       <c r="O293" s="5" t="n">
-        <v>19.814961</v>
+        <v>0.09698900000000001</v>
       </c>
       <c r="P293" s="5" t="n">
-        <v>7.78393</v>
-      </c>
-      <c r="Q293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.856599</v>
+      </c>
+      <c r="Q293" s="5" t="n">
+        <v>0.401247</v>
       </c>
       <c r="R293" t="inlineStr">
         <is>
@@ -32628,19 +32526,15 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>General and administrative 20</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Accretion of asset retirement obligation 13</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -32691,16 +32585,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O294" s="5" t="n">
-        <v>1.133742</v>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P294" s="5" t="n">
-        <v>2.110059</v>
-      </c>
-      <c r="Q294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.026501</v>
+      </c>
+      <c r="Q294" s="5" t="n">
+        <v>-0.02311</v>
       </c>
       <c r="R294" t="inlineStr">
         <is>
@@ -32716,15 +32610,19 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Share-based compensation 17, 19</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr"/>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -32775,16 +32673,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O295" s="5" t="n">
-        <v>0.7417899999999999</v>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P295" s="5" t="n">
-        <v>1.458031</v>
-      </c>
-      <c r="Q295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.004807</v>
+      </c>
+      <c r="Q295" s="5" t="n">
+        <v>0.037405</v>
       </c>
       <c r="R295" t="inlineStr">
         <is>
@@ -32800,15 +32698,19 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Property maintenance 20</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr"/>
+          <t>Interest expense 27</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -32859,16 +32761,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O296" s="5" t="n">
-        <v>0.228486</v>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P296" s="5" t="n">
-        <v>0.504178</v>
-      </c>
-      <c r="Q296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.35776</v>
+      </c>
+      <c r="Q296" s="5" t="n">
+        <v>-0.173124</v>
       </c>
       <c r="R296" t="inlineStr">
         <is>
@@ -32884,19 +32786,15 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Depreciation 8</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Gain on disposal of equipment</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -32942,19 +32840,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N297" s="5" t="n">
-        <v>0.015821</v>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O297" s="5" t="n">
-        <v>0.032443</v>
-      </c>
-      <c r="P297" s="5" t="n">
-        <v>0.062081</v>
-      </c>
-      <c r="Q297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.001504</v>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q297" s="5" t="n">
+        <v>0.005496</v>
       </c>
       <c r="R297" t="inlineStr">
         <is>
@@ -32970,15 +32870,19 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Accretion of asset retirement obligation 12</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr"/>
+          <t>Total other income</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
@@ -33029,16 +32933,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O298" s="5" t="n">
-        <v>0.017619</v>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P298" s="5" t="n">
-        <v>0.026501</v>
-      </c>
-      <c r="Q298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.86957</v>
+      </c>
+      <c r="Q298" s="5" t="n">
+        <v>3.192511</v>
       </c>
       <c r="R298" t="inlineStr">
         <is>
@@ -33059,10 +32963,14 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Flow-through premium income 15, 26</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr"/>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -33114,15 +33022,13 @@
         </is>
       </c>
       <c r="O299" s="5" t="n">
-        <v>0.332704</v>
+        <v>-21.96958</v>
       </c>
       <c r="P299" s="5" t="n">
-        <v>2.392425</v>
-      </c>
-      <c r="Q299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-9.721878999999999</v>
+      </c>
+      <c r="Q299" s="5" t="n">
+        <v>-16.267727</v>
       </c>
       <c r="R299" t="inlineStr">
         <is>
@@ -33143,12 +33049,12 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
+          <t>Basic and diluted loss per common share 17 $</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -33201,16 +33107,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O300" s="5" t="n">
-        <v>-0.027558</v>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P300" s="5" t="n">
-        <v>0.004807</v>
-      </c>
-      <c r="Q300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.999999999999999e-08</v>
+      </c>
+      <c r="Q300" s="5" t="n">
+        <v>1e-07</v>
       </c>
       <c r="R300" t="inlineStr">
         <is>
@@ -33226,19 +33132,15 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>outstanding shares</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Interest expense 7</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -33289,16 +33191,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O301" s="5" t="n">
-        <v>-0.064814</v>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P301" s="5" t="n">
-        <v>-0.35776</v>
-      </c>
-      <c r="Q301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>160.9653</v>
+      </c>
+      <c r="Q301" s="5" t="n">
+        <v>170.766096</v>
       </c>
       <c r="R301" t="inlineStr">
         <is>
@@ -33314,12 +33216,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Total other income (loss)</t>
+          <t>Exploration and evaluation 10, 20, 21 $</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -33374,10 +33276,10 @@
         </is>
       </c>
       <c r="O302" s="5" t="n">
-        <v>0.338825</v>
+        <v>19.814961</v>
       </c>
       <c r="P302" s="5" t="n">
-        <v>2.896071</v>
+        <v>7.78393</v>
       </c>
       <c r="Q302" t="inlineStr">
         <is>
@@ -33398,17 +33300,17 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share 15 $</t>
+          <t>General and administrative 20</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -33462,10 +33364,10 @@
         </is>
       </c>
       <c r="O303" s="5" t="n">
-        <v>2.63e-07</v>
+        <v>1.133742</v>
       </c>
       <c r="P303" s="5" t="n">
-        <v>6.1e-08</v>
+        <v>2.110059</v>
       </c>
       <c r="Q303" t="inlineStr">
         <is>
@@ -33486,12 +33388,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Weighted average number of outstanding shares</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
+          <t>Share-based compensation 17, 19</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -33546,10 +33448,10 @@
         </is>
       </c>
       <c r="O304" s="5" t="n">
-        <v>83.666459</v>
+        <v>0.7417899999999999</v>
       </c>
       <c r="P304" s="5" t="n">
-        <v>160.9653</v>
+        <v>1.458031</v>
       </c>
       <c r="Q304" t="inlineStr">
         <is>
@@ -33575,7 +33477,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Exploration and evaluation 19 $</t>
+          <t>Property maintenance 20</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -33624,16 +33526,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N305" s="5" t="n">
-        <v>3.771965</v>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O305" s="5" t="n">
-        <v>19.814961</v>
-      </c>
-      <c r="P305" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.228486</v>
+      </c>
+      <c r="P305" s="5" t="n">
+        <v>0.504178</v>
       </c>
       <c r="Q305" t="inlineStr">
         <is>
@@ -33659,12 +33561,12 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>General and administrative 19</t>
+          <t>Depreciation 8</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -33713,15 +33615,13 @@
         </is>
       </c>
       <c r="N306" s="5" t="n">
-        <v>0.642689</v>
+        <v>0.015821</v>
       </c>
       <c r="O306" s="5" t="n">
-        <v>1.133742</v>
-      </c>
-      <c r="P306" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.032443</v>
+      </c>
+      <c r="P306" s="5" t="n">
+        <v>0.062081</v>
       </c>
       <c r="Q306" t="inlineStr">
         <is>
@@ -33747,7 +33647,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Listing costs 3</t>
+          <t>Accretion of asset retirement obligation 12</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
@@ -33796,18 +33696,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N307" s="5" t="n">
-        <v>1.255151</v>
-      </c>
-      <c r="O307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O307" s="5" t="n">
+        <v>0.017619</v>
+      </c>
+      <c r="P307" s="5" t="n">
+        <v>0.026501</v>
       </c>
       <c r="Q307" t="inlineStr">
         <is>
@@ -33828,12 +33726,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Share-based compensation 16, 18</t>
+          <t>Flow-through premium income 15, 26</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
@@ -33882,16 +33780,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N308" s="5" t="n">
-        <v>0.643252</v>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O308" s="5" t="n">
-        <v>0.7417899999999999</v>
-      </c>
-      <c r="P308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.332704</v>
+      </c>
+      <c r="P308" s="5" t="n">
+        <v>2.392425</v>
       </c>
       <c r="Q308" t="inlineStr">
         <is>
@@ -33912,15 +33810,19 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Property maintenance 19</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr"/>
+          <t>Foreign exchange gain (loss)</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -33966,16 +33868,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N309" s="5" t="n">
-        <v>0.199717</v>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O309" s="5" t="n">
-        <v>0.228486</v>
-      </c>
-      <c r="P309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.027558</v>
+      </c>
+      <c r="P309" s="5" t="n">
+        <v>0.004807</v>
       </c>
       <c r="Q309" t="inlineStr">
         <is>
@@ -33996,15 +33898,19 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Accretion of asset retirement obligation 11</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>Interest expense 7</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -34050,16 +33956,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N310" s="5" t="n">
-        <v>0.017185</v>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O310" s="5" t="n">
-        <v>0.017619</v>
-      </c>
-      <c r="P310" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.064814</v>
+      </c>
+      <c r="P310" s="5" t="n">
+        <v>-0.35776</v>
       </c>
       <c r="Q310" t="inlineStr">
         <is>
@@ -34080,19 +33986,15 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Total other income (loss)</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
@@ -34138,16 +34040,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N311" s="5" t="n">
-        <v>0.00027</v>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O311" s="5" t="n">
-        <v>-0.027558</v>
-      </c>
-      <c r="P311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.338825</v>
+      </c>
+      <c r="P311" s="5" t="n">
+        <v>2.896071</v>
       </c>
       <c r="Q311" t="inlineStr">
         <is>
@@ -34168,15 +34070,19 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Flow-through premium 14, 24</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr"/>
+          <t>Basic and diluted loss per common share 15 $</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -34222,16 +34128,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N312" s="5" t="n">
-        <v>0.027984</v>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O312" s="5" t="n">
-        <v>0.332704</v>
-      </c>
-      <c r="P312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.63e-07</v>
+      </c>
+      <c r="P312" s="5" t="n">
+        <v>6.1e-08</v>
       </c>
       <c r="Q312" t="inlineStr">
         <is>
@@ -34252,12 +34158,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Weighted average number of outstanding shares</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Basic and diluted</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
@@ -34306,18 +34212,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N313" s="5" t="n">
-        <v>0.041249</v>
-      </c>
-      <c r="O313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O313" s="5" t="n">
+        <v>83.666459</v>
+      </c>
+      <c r="P313" s="5" t="n">
+        <v>160.9653</v>
       </c>
       <c r="Q313" t="inlineStr">
         <is>
@@ -34338,19 +34242,15 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation 19 $</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -34397,10 +34297,10 @@
         </is>
       </c>
       <c r="N314" s="5" t="n">
-        <v>0.001811</v>
+        <v>3.771965</v>
       </c>
       <c r="O314" s="5" t="n">
-        <v>0.09698900000000001</v>
+        <v>19.814961</v>
       </c>
       <c r="P314" t="inlineStr">
         <is>
@@ -34426,17 +34326,17 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Interest expense 7</t>
+          <t>General and administrative 19</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -34484,13 +34384,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N315" s="5" t="n">
+        <v>0.642689</v>
       </c>
       <c r="O315" s="5" t="n">
-        <v>-0.064814</v>
+        <v>1.133742</v>
       </c>
       <c r="P315" t="inlineStr">
         <is>
@@ -34516,12 +34414,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Gain on disposal of equipment</t>
+          <t>Listing costs 3</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
@@ -34570,13 +34468,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O316" s="5" t="n">
-        <v>0.001504</v>
+      <c r="N316" s="5" t="n">
+        <v>1.255151</v>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P316" t="inlineStr">
         <is>
@@ -34602,12 +34500,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Total other income (loss)</t>
+          <t>Share-based compensation 16, 18</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
@@ -34657,10 +34555,10 @@
         </is>
       </c>
       <c r="N317" s="5" t="n">
-        <v>0.071314</v>
+        <v>0.643252</v>
       </c>
       <c r="O317" s="5" t="n">
-        <v>0.338825</v>
+        <v>0.7417899999999999</v>
       </c>
       <c r="P317" t="inlineStr">
         <is>
@@ -34686,19 +34584,15 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Property maintenance 19</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -34745,10 +34639,10 @@
         </is>
       </c>
       <c r="N318" s="5" t="n">
-        <v>-6.762966</v>
+        <v>0.199717</v>
       </c>
       <c r="O318" s="5" t="n">
-        <v>-21.96958</v>
+        <v>0.228486</v>
       </c>
       <c r="P318" t="inlineStr">
         <is>
@@ -34774,12 +34668,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Basic loss per common share 15 $</t>
+          <t>Accretion of asset retirement obligation 11</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
@@ -34829,10 +34723,10 @@
         </is>
       </c>
       <c r="N319" s="5" t="n">
-        <v>1.15e-07</v>
+        <v>0.017185</v>
       </c>
       <c r="O319" s="5" t="n">
-        <v>2.63e-07</v>
+        <v>0.017619</v>
       </c>
       <c r="P319" t="inlineStr">
         <is>
@@ -34858,15 +34752,19 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Weighted average number of outstanding shares</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr"/>
+          <t>Foreign exchange gain (loss)</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -34913,10 +34811,10 @@
         </is>
       </c>
       <c r="N320" s="5" t="n">
-        <v>58.698031</v>
+        <v>0.00027</v>
       </c>
       <c r="O320" s="5" t="n">
-        <v>83.666459</v>
+        <v>-0.027558</v>
       </c>
       <c r="P320" t="inlineStr">
         <is>
@@ -34942,57 +34840,65 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Bank charges</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Flow-through premium 14, 24</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F321" s="5" t="n">
-        <v>0.000203</v>
-      </c>
-      <c r="G321" s="5" t="n">
-        <v>0.000113</v>
-      </c>
-      <c r="H321" s="5" t="n">
-        <v>0.000275</v>
-      </c>
-      <c r="I321" s="5" t="n">
-        <v>0.000112</v>
-      </c>
-      <c r="J321" s="5" t="n">
-        <v>0.000112</v>
-      </c>
-      <c r="K321" s="5" t="n">
-        <v>0.000107</v>
-      </c>
-      <c r="L321" s="5" t="n">
-        <v>0.000255</v>
-      </c>
-      <c r="M321" s="5" t="n">
-        <v>0.000549</v>
-      </c>
-      <c r="N321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N321" s="5" t="n">
+        <v>0.027984</v>
+      </c>
+      <c r="O321" s="5" t="n">
+        <v>0.332704</v>
       </c>
       <c r="P321" t="inlineStr">
         <is>
@@ -35018,12 +34924,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Legal and accounting fees</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -35032,34 +34938,48 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F322" s="5" t="n">
-        <v>0.04149</v>
-      </c>
-      <c r="G322" s="5" t="n">
-        <v>0.123559</v>
-      </c>
-      <c r="H322" s="5" t="n">
-        <v>0.297439</v>
-      </c>
-      <c r="I322" s="5" t="n">
-        <v>0.080775</v>
-      </c>
-      <c r="J322" s="5" t="n">
-        <v>0.038486</v>
-      </c>
-      <c r="K322" s="5" t="n">
-        <v>0.032337</v>
-      </c>
-      <c r="L322" s="5" t="n">
-        <v>0.05281</v>
-      </c>
-      <c r="M322" s="5" t="n">
-        <v>0.060961</v>
-      </c>
-      <c r="N322" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N322" s="5" t="n">
+        <v>0.041249</v>
       </c>
       <c r="O322" t="inlineStr">
         <is>
@@ -35090,17 +35010,17 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Regulatory fees</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -35113,36 +35033,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G323" s="5" t="n">
-        <v>0.004352</v>
-      </c>
-      <c r="H323" s="5" t="n">
-        <v>0.020686</v>
-      </c>
-      <c r="I323" s="5" t="n">
-        <v>0.006135</v>
-      </c>
-      <c r="J323" s="5" t="n">
-        <v>0.005962</v>
-      </c>
-      <c r="K323" s="5" t="n">
-        <v>0.007065</v>
-      </c>
-      <c r="L323" s="5" t="n">
-        <v>0.004238</v>
-      </c>
-      <c r="M323" s="5" t="n">
-        <v>0.005652</v>
-      </c>
-      <c r="N323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N323" s="5" t="n">
+        <v>0.001811</v>
+      </c>
+      <c r="O323" s="5" t="n">
+        <v>0.09698900000000001</v>
       </c>
       <c r="P323" t="inlineStr">
         <is>
@@ -35168,22 +35098,28 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr"/>
+          <t>Interest expense 7</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F324" s="5" t="n">
-        <v>0.07785499999999999</v>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
@@ -35210,8 +35146,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L324" s="5" t="n">
-        <v>0.02153</v>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M324" t="inlineStr">
         <is>
@@ -35223,10 +35161,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O324" s="5" t="n">
+        <v>-0.064814</v>
       </c>
       <c r="P324" t="inlineStr">
         <is>
@@ -35252,19 +35188,15 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Transfer agent</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Gain on disposal of equipment</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -35275,36 +35207,48 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G325" s="5" t="n">
-        <v>0.009505</v>
-      </c>
-      <c r="H325" s="5" t="n">
-        <v>0.008697999999999999</v>
-      </c>
-      <c r="I325" s="5" t="n">
-        <v>0.007012</v>
-      </c>
-      <c r="J325" s="5" t="n">
-        <v>0.005787</v>
-      </c>
-      <c r="K325" s="5" t="n">
-        <v>0.007383</v>
-      </c>
-      <c r="L325" s="5" t="n">
-        <v>0.011615</v>
-      </c>
-      <c r="M325" s="5" t="n">
-        <v>0.007509</v>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N325" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O325" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O325" s="5" t="n">
+        <v>0.001504</v>
       </c>
       <c r="P325" t="inlineStr">
         <is>
@@ -35330,19 +35274,15 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Net and comprehensive income (loss) for the year</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Total other income (loss)</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
           <t>-</t>
@@ -35363,30 +35303,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I326" s="5" t="n">
-        <v>-0.09619900000000001</v>
-      </c>
-      <c r="J326" s="5" t="n">
-        <v>-0.06390700000000001</v>
-      </c>
-      <c r="K326" s="5" t="n">
-        <v>-0.047507</v>
-      </c>
-      <c r="L326" s="5" t="n">
-        <v>-0.090448</v>
-      </c>
-      <c r="M326" s="5" t="n">
-        <v>-0.074671</v>
-      </c>
-      <c r="N326" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O326" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N326" s="5" t="n">
+        <v>0.071314</v>
+      </c>
+      <c r="O326" s="5" t="n">
+        <v>0.338825</v>
       </c>
       <c r="P326" t="inlineStr">
         <is>
@@ -35412,15 +35358,19 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Retained earnings (deficit), beginning of year</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr"/>
+          <t>Net and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
@@ -35441,30 +35391,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I327" s="5" t="n">
-        <v>-0.5960760000000001</v>
-      </c>
-      <c r="J327" s="5" t="n">
-        <v>-0.692275</v>
-      </c>
-      <c r="K327" s="5" t="n">
-        <v>-0.756182</v>
-      </c>
-      <c r="L327" s="5" t="n">
-        <v>-0.803689</v>
-      </c>
-      <c r="M327" s="5" t="n">
-        <v>-0.894137</v>
-      </c>
-      <c r="N327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N327" s="5" t="n">
+        <v>-6.762966</v>
+      </c>
+      <c r="O327" s="5" t="n">
+        <v>-21.96958</v>
       </c>
       <c r="P327" t="inlineStr">
         <is>
@@ -35490,12 +35446,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Retained earnings (deficit), end of year</t>
+          <t>Basic loss per common share 15 $</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
@@ -35519,30 +35475,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I328" s="5" t="n">
-        <v>-0.692275</v>
-      </c>
-      <c r="J328" s="5" t="n">
-        <v>-0.756182</v>
-      </c>
-      <c r="K328" s="5" t="n">
-        <v>-0.803689</v>
-      </c>
-      <c r="L328" s="5" t="n">
-        <v>-0.894137</v>
-      </c>
-      <c r="M328" s="5" t="n">
-        <v>-0.968808</v>
-      </c>
-      <c r="N328" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O328" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N328" s="5" t="n">
+        <v>1.15e-07</v>
+      </c>
+      <c r="O328" s="5" t="n">
+        <v>2.63e-07</v>
       </c>
       <c r="P328" t="inlineStr">
         <is>
@@ -35568,19 +35530,15 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of outstanding shares</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Net income (loss) per share, basic and diluted</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
           <t>-</t>
@@ -35601,30 +35559,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I329" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="J329" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="K329" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="L329" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="M329" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="N329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N329" s="5" t="n">
+        <v>58.698031</v>
+      </c>
+      <c r="O329" s="5" t="n">
+        <v>83.666459</v>
       </c>
       <c r="P329" t="inlineStr">
         <is>
@@ -35655,12 +35619,12 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Bank charges</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -35668,35 +35632,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F330" s="5" t="n">
+        <v>0.000203</v>
+      </c>
+      <c r="G330" s="5" t="n">
+        <v>0.000113</v>
+      </c>
+      <c r="H330" s="5" t="n">
+        <v>0.000275</v>
       </c>
       <c r="I330" s="5" t="n">
-        <v>4.8275</v>
+        <v>0.000112</v>
       </c>
       <c r="J330" s="5" t="n">
-        <v>4.8275</v>
+        <v>0.000112</v>
       </c>
       <c r="K330" s="5" t="n">
-        <v>4.8275</v>
+        <v>0.000107</v>
       </c>
       <c r="L330" s="5" t="n">
-        <v>5.458446</v>
+        <v>0.000255</v>
       </c>
       <c r="M330" s="5" t="n">
-        <v>5.458446</v>
+        <v>0.000549</v>
       </c>
       <c r="N330" t="inlineStr">
         <is>
@@ -35737,48 +35695,38 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Legal and accounting fees</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F331" s="5" t="n">
+        <v>0.04149</v>
       </c>
       <c r="G331" s="5" t="n">
-        <v>0.002288</v>
+        <v>0.123559</v>
       </c>
       <c r="H331" s="5" t="n">
-        <v>0.004822</v>
+        <v>0.297439</v>
       </c>
       <c r="I331" s="5" t="n">
-        <v>0.002165</v>
+        <v>0.080775</v>
       </c>
       <c r="J331" s="5" t="n">
-        <v>0.01356</v>
+        <v>0.038486</v>
       </c>
       <c r="K331" s="5" t="n">
-        <v>0.000615</v>
-      </c>
-      <c r="L331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.032337</v>
+      </c>
+      <c r="L331" s="5" t="n">
+        <v>0.05281</v>
+      </c>
+      <c r="M331" s="5" t="n">
+        <v>0.060961</v>
       </c>
       <c r="N331" t="inlineStr">
         <is>
@@ -35819,10 +35767,14 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Share-based compensation (Notes 4 and 9)</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr"/>
+          <t>Regulatory fees</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>
@@ -35833,38 +35785,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G332" s="5" t="n">
+        <v>0.004352</v>
+      </c>
+      <c r="H332" s="5" t="n">
+        <v>0.020686</v>
+      </c>
+      <c r="I332" s="5" t="n">
+        <v>0.006135</v>
+      </c>
+      <c r="J332" s="5" t="n">
+        <v>0.005962</v>
+      </c>
+      <c r="K332" s="5" t="n">
+        <v>0.007065</v>
       </c>
       <c r="L332" s="5" t="n">
-        <v>0.02153</v>
-      </c>
-      <c r="M332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.004238</v>
+      </c>
+      <c r="M332" s="5" t="n">
+        <v>0.005652</v>
       </c>
       <c r="N332" t="inlineStr">
         <is>
@@ -35905,29 +35845,27 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Rent</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G333" s="5" t="n">
-        <v>0.00525</v>
-      </c>
-      <c r="H333" s="5" t="n">
-        <v>0.006782</v>
+      <c r="F333" s="5" t="n">
+        <v>0.07785499999999999</v>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
@@ -35944,10 +35882,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L333" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L333" s="5" t="n">
+        <v>0.02153</v>
       </c>
       <c r="M333" t="inlineStr">
         <is>
@@ -35993,46 +35929,44 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Income (loss) before other item</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr"/>
+          <t>Transfer agent</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F334" s="5" t="n">
-        <v>-0.119548</v>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G334" s="5" t="n">
-        <v>-0.145067</v>
+        <v>0.009505</v>
       </c>
       <c r="H334" s="5" t="n">
-        <v>-0.338702</v>
+        <v>0.008697999999999999</v>
       </c>
       <c r="I334" s="5" t="n">
-        <v>-0.09619900000000001</v>
-      </c>
-      <c r="J334" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K334" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L334" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M334" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.007012</v>
+      </c>
+      <c r="J334" s="5" t="n">
+        <v>0.005787</v>
+      </c>
+      <c r="K334" s="5" t="n">
+        <v>0.007383</v>
+      </c>
+      <c r="L334" s="5" t="n">
+        <v>0.011615</v>
+      </c>
+      <c r="M334" s="5" t="n">
+        <v>0.007509</v>
       </c>
       <c r="N334" t="inlineStr">
         <is>
@@ -36068,53 +36002,53 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Other item</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Interest</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr"/>
+          <t>Net and comprehensive income (loss) for the year</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F335" s="5" t="n">
-        <v>0.002707</v>
-      </c>
-      <c r="G335" s="5" t="n">
-        <v>0.005293</v>
-      </c>
-      <c r="H335" s="5" t="n">
-        <v>0.00131</v>
-      </c>
-      <c r="I335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I335" s="5" t="n">
+        <v>-0.09619900000000001</v>
+      </c>
+      <c r="J335" s="5" t="n">
+        <v>-0.06390700000000001</v>
+      </c>
+      <c r="K335" s="5" t="n">
+        <v>-0.047507</v>
+      </c>
+      <c r="L335" s="5" t="n">
+        <v>-0.090448</v>
+      </c>
+      <c r="M335" s="5" t="n">
+        <v>-0.074671</v>
       </c>
       <c r="N335" t="inlineStr">
         <is>
@@ -36150,55 +36084,49 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Other item</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Net and comprehensive income (loss) for the year</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Retained earnings (deficit), beginning of year</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F336" s="5" t="n">
-        <v>-0.116841</v>
-      </c>
-      <c r="G336" s="5" t="n">
-        <v>-0.139774</v>
-      </c>
-      <c r="H336" s="5" t="n">
-        <v>-0.337392</v>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I336" s="5" t="n">
-        <v>-0.09619900000000001</v>
-      </c>
-      <c r="J336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.5960760000000001</v>
+      </c>
+      <c r="J336" s="5" t="n">
+        <v>-0.692275</v>
+      </c>
+      <c r="K336" s="5" t="n">
+        <v>-0.756182</v>
+      </c>
+      <c r="L336" s="5" t="n">
+        <v>-0.803689</v>
+      </c>
+      <c r="M336" s="5" t="n">
+        <v>-0.894137</v>
       </c>
       <c r="N336" t="inlineStr">
         <is>
@@ -36234,12 +36162,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Other item</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Retained earnings (deficit), beginning of year</t>
+          <t>Retained earnings (deficit), end of year</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
@@ -36248,37 +36176,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F337" s="5" t="n">
-        <v>-0.002069</v>
-      </c>
-      <c r="G337" s="5" t="n">
-        <v>-0.11891</v>
-      </c>
-      <c r="H337" s="5" t="n">
-        <v>-0.258684</v>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I337" s="5" t="n">
-        <v>-0.5960760000000001</v>
-      </c>
-      <c r="J337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.692275</v>
+      </c>
+      <c r="J337" s="5" t="n">
+        <v>-0.756182</v>
+      </c>
+      <c r="K337" s="5" t="n">
+        <v>-0.803689</v>
+      </c>
+      <c r="L337" s="5" t="n">
+        <v>-0.894137</v>
+      </c>
+      <c r="M337" s="5" t="n">
+        <v>-0.968808</v>
       </c>
       <c r="N337" t="inlineStr">
         <is>
@@ -36314,51 +36240,53 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Other item</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Retained earnings (deficit), end of year</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
+          <t>Net income (loss) per share, basic and diluted</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F338" s="5" t="n">
-        <v>-0.11891</v>
-      </c>
-      <c r="G338" s="5" t="n">
-        <v>-0.258684</v>
-      </c>
-      <c r="H338" s="5" t="n">
-        <v>-0.5960760000000001</v>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I338" s="5" t="n">
-        <v>-0.692275</v>
-      </c>
-      <c r="J338" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K338" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L338" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M338" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2e-08</v>
+      </c>
+      <c r="J338" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="K338" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="L338" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="M338" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="N338" t="inlineStr">
         <is>
@@ -36394,17 +36322,17 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Other item</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Net income (loss) per share, basic and diluted</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>SharesOutstanding</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -36412,37 +36340,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F339" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="G339" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="H339" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I339" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="J339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.8275</v>
+      </c>
+      <c r="J339" s="5" t="n">
+        <v>4.8275</v>
+      </c>
+      <c r="K339" s="5" t="n">
+        <v>4.8275</v>
+      </c>
+      <c r="L339" s="5" t="n">
+        <v>5.458446</v>
+      </c>
+      <c r="M339" s="5" t="n">
+        <v>5.458446</v>
       </c>
       <c r="N339" t="inlineStr">
         <is>
@@ -36478,17 +36404,17 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Other item</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -36496,27 +36422,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F340" s="5" t="n">
-        <v>3.387075</v>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G340" s="5" t="n">
-        <v>5.0775</v>
+        <v>0.002288</v>
       </c>
       <c r="H340" s="5" t="n">
-        <v>5.221237</v>
+        <v>0.004822</v>
       </c>
       <c r="I340" s="5" t="n">
-        <v>4.8275</v>
-      </c>
-      <c r="J340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002165</v>
+      </c>
+      <c r="J340" s="5" t="n">
+        <v>0.01356</v>
+      </c>
+      <c r="K340" s="5" t="n">
+        <v>0.000615</v>
       </c>
       <c r="L340" t="inlineStr">
         <is>
@@ -36562,12 +36486,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Other item</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>220,016 (96,199) 123,817 Total equity $ 507,408 50,000</t>
+          <t>Share-based compensation (Notes 4 and 9)</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
@@ -36586,8 +36510,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H341" s="5" t="n">
-        <v>-0.337392</v>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
@@ -36604,10 +36530,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L341" s="5" t="n">
+        <v>0.02153</v>
       </c>
       <c r="M341" t="inlineStr">
         <is>
@@ -36648,15 +36572,19 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Other item</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Retained earnings (deficit) $ (258,684) - - (337,392) (596,076)</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr"/>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>-</t>
@@ -36667,16 +36595,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G342" s="5" t="n">
+        <v>0.00525</v>
       </c>
       <c r="H342" s="5" t="n">
-        <v>-0.692275</v>
-      </c>
-      <c r="I342" s="5" t="n">
-        <v>-0.09619900000000001</v>
+        <v>0.006782</v>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
@@ -36732,12 +36660,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Other item</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>reserve $ 105,428 (26,245) Share-based payments - - 79,183</t>
+          <t>Income (loss) before other item</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
@@ -36746,23 +36674,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F343" s="5" t="n">
+        <v>-0.119548</v>
+      </c>
+      <c r="G343" s="5" t="n">
+        <v>-0.145067</v>
       </c>
       <c r="H343" s="5" t="n">
-        <v>0.079183</v>
-      </c>
-      <c r="I343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.338702</v>
+      </c>
+      <c r="I343" s="5" t="n">
+        <v>-0.09619900000000001</v>
       </c>
       <c r="J343" t="inlineStr">
         <is>
@@ -36823,7 +36745,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>shares Amount $ 660,664 76,245 - - 736,909</t>
+          <t>Interest</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
@@ -36832,18 +36754,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F344" s="5" t="n">
+        <v>0.002707</v>
+      </c>
+      <c r="G344" s="5" t="n">
+        <v>0.005293</v>
       </c>
       <c r="H344" s="5" t="n">
-        <v>0.736909</v>
+        <v>0.00131</v>
       </c>
       <c r="I344" t="inlineStr">
         <is>
@@ -36904,17 +36822,17 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other item</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Loss before other item</t>
+          <t>Net and comprehensive income (loss) for the year</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -36922,21 +36840,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F345" s="5" t="n">
+        <v>-0.116841</v>
       </c>
       <c r="G345" s="5" t="n">
-        <v>-0.145067</v>
+        <v>-0.139774</v>
       </c>
       <c r="H345" s="5" t="n">
-        <v>-0.338702</v>
-      </c>
-      <c r="I345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.337392</v>
+      </c>
+      <c r="I345" s="5" t="n">
+        <v>-0.09619900000000001</v>
       </c>
       <c r="J345" t="inlineStr">
         <is>
@@ -36997,34 +36911,26 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Retained earnings (deficit), beginning of year</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F346" s="5" t="n">
+        <v>-0.002069</v>
       </c>
       <c r="G346" s="5" t="n">
-        <v>-0.139774</v>
+        <v>-0.11891</v>
       </c>
       <c r="H346" s="5" t="n">
-        <v>-0.337392</v>
-      </c>
-      <c r="I346" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.258684</v>
+      </c>
+      <c r="I346" s="5" t="n">
+        <v>-0.5960760000000001</v>
       </c>
       <c r="J346" t="inlineStr">
         <is>
@@ -37085,34 +36991,26 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Net loss per share, basic and diluted</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Retained earnings (deficit), end of year</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F347" s="5" t="n">
+        <v>-0.11891</v>
       </c>
       <c r="G347" s="5" t="n">
-        <v>-3e-08</v>
+        <v>-0.258684</v>
       </c>
       <c r="H347" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
-      </c>
-      <c r="I347" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.5960760000000001</v>
+      </c>
+      <c r="I347" s="5" t="n">
+        <v>-0.692275</v>
       </c>
       <c r="J347" t="inlineStr">
         <is>
@@ -37173,30 +37071,30 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Total equity $ 647,182 507,408 50,000 - 220,016</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr"/>
+          <t>Net income (loss) per share, basic and diluted</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F348" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="G348" s="5" t="n">
-        <v>-0.337392</v>
+        <v>-3e-08</v>
       </c>
       <c r="H348" s="5" t="n">
-        <v>-0.139774</v>
-      </c>
-      <c r="I348" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="I348" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="J348" t="inlineStr">
         <is>
@@ -37257,30 +37155,30 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Deficit $ - - (118,910) (139,774) (258,684)</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F349" s="5" t="n">
+        <v>3.387075</v>
       </c>
       <c r="G349" s="5" t="n">
-        <v>-0.5960760000000001</v>
+        <v>5.0775</v>
       </c>
       <c r="H349" s="5" t="n">
-        <v>-0.337392</v>
-      </c>
-      <c r="I349" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.221237</v>
+      </c>
+      <c r="I349" s="5" t="n">
+        <v>4.8275</v>
       </c>
       <c r="J349" t="inlineStr">
         <is>
@@ -37341,7 +37239,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>reserve $ 105,428 - 105,428 (26,245) Share-based payments -</t>
+          <t>220,016 (96,199) 123,817 Total equity $ 507,408 50,000</t>
         </is>
       </c>
       <c r="D350" t="inlineStr"/>
@@ -37355,13 +37253,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G350" s="5" t="n">
-        <v>0.079183</v>
-      </c>
-      <c r="H350" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H350" s="5" t="n">
+        <v>-0.337392</v>
       </c>
       <c r="I350" t="inlineStr">
         <is>
@@ -37427,7 +37325,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Amount $ 660,664 - 660,664 76,245 -</t>
+          <t>Retained earnings (deficit) $ (258,684) - - (337,392) (596,076)</t>
         </is>
       </c>
       <c r="D351" t="inlineStr"/>
@@ -37441,18 +37339,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G351" s="5" t="n">
-        <v>0.736909</v>
-      </c>
-      <c r="H351" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I351" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H351" s="5" t="n">
+        <v>-0.692275</v>
+      </c>
+      <c r="I351" s="5" t="n">
+        <v>-0.09619900000000001</v>
       </c>
       <c r="J351" t="inlineStr">
         <is>
@@ -37508,12 +37404,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>shares</t>
+          <t>Other item</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>shares total</t>
+          <t>reserve $ 105,428 (26,245) Share-based payments - - 79,183</t>
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
@@ -37532,10 +37428,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H352" s="5" t="n">
+        <v>0.079183</v>
       </c>
       <c r="I352" t="inlineStr">
         <is>
@@ -37601,7 +37495,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>77,855 647,182 507,408 (116,841) (139,774) Total equity $ 137,931 600,000</t>
+          <t>shares Amount $ 660,664 76,245 - - 736,909</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
@@ -37610,16 +37504,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F353" s="5" t="n">
-        <v>-0.177263</v>
-      </c>
-      <c r="G353" s="5" t="n">
-        <v>0.1255</v>
-      </c>
-      <c r="H353" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H353" s="5" t="n">
+        <v>0.736909</v>
       </c>
       <c r="I353" t="inlineStr">
         <is>
@@ -37680,15 +37576,19 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Other item</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Other item total</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr"/>
+          <t>Loss before other item</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>
@@ -37699,15 +37599,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H354" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G354" s="5" t="n">
+        <v>-0.145067</v>
+      </c>
+      <c r="H354" s="5" t="n">
+        <v>-0.338702</v>
       </c>
       <c r="I354" t="inlineStr">
         <is>
@@ -37773,25 +37669,29 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>(2,069) Retained earnings (deficit) (116,841) (118,910)</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>Net and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F355" s="5" t="n">
-        <v>-0.258684</v>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G355" s="5" t="n">
         <v>-0.139774</v>
       </c>
-      <c r="H355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H355" s="5" t="n">
+        <v>-0.337392</v>
       </c>
       <c r="I355" t="inlineStr">
         <is>
@@ -37857,27 +37757,29 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Share-based payments reserve $ - - - 27,573 77,855 - 105,428</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>Net loss per share, basic and diluted</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F356" s="5" t="n">
-        <v>0.105428</v>
-      </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H356" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G356" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="H356" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
       </c>
       <c r="I356" t="inlineStr">
         <is>
@@ -37943,7 +37845,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>- - 660,664 - 660,664 Amount $ 140,000 600,000</t>
+          <t>Total equity $ 647,182 507,408 50,000 - 220,016</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
@@ -37952,16 +37854,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F357" s="5" t="n">
-        <v>-0.204836</v>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G357" s="5" t="n">
-        <v>0.1255</v>
-      </c>
-      <c r="H357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.337392</v>
+      </c>
+      <c r="H357" s="5" t="n">
+        <v>-0.139774</v>
       </c>
       <c r="I357" t="inlineStr">
         <is>
@@ -38022,12 +37924,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>shares</t>
+          <t>Other item</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>shares</t>
+          <t>Deficit $ - - (118,910) (139,774) (258,684)</t>
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
@@ -38041,15 +37943,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H358" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G358" s="5" t="n">
+        <v>-0.5960760000000001</v>
+      </c>
+      <c r="H358" s="5" t="n">
+        <v>-0.337392</v>
       </c>
       <c r="I358" t="inlineStr">
         <is>
@@ -38097,6 +37995,1380 @@
         </is>
       </c>
       <c r="R358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Other item</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>reserve $ 105,428 - 105,428 (26,245) Share-based payments -</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G359" s="5" t="n">
+        <v>0.079183</v>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Other item</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Amount $ 660,664 - 660,664 76,245 -</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr"/>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G360" s="5" t="n">
+        <v>0.736909</v>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>shares</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>shares total</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr"/>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Other item</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>77,855 647,182 507,408 (116,841) (139,774) Total equity $ 137,931 600,000</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr"/>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F362" s="5" t="n">
+        <v>-0.177263</v>
+      </c>
+      <c r="G362" s="5" t="n">
+        <v>0.1255</v>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Other item</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Other item total</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr"/>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Other item</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>(2,069) Retained earnings (deficit) (116,841) (118,910)</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr"/>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F364" s="5" t="n">
+        <v>-0.258684</v>
+      </c>
+      <c r="G364" s="5" t="n">
+        <v>-0.139774</v>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Other item</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Share-based payments reserve $ - - - 27,573 77,855 - 105,428</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr"/>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F365" s="5" t="n">
+        <v>0.105428</v>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Other item</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>- - 660,664 - 660,664 Amount $ 140,000 600,000</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr"/>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F366" s="5" t="n">
+        <v>-0.204836</v>
+      </c>
+      <c r="G366" s="5" t="n">
+        <v>0.1255</v>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>shares</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>shares</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr"/>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Bank charges $</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E368" s="5" t="n">
+        <v>9.1e-05</v>
+      </c>
+      <c r="F368" s="5" t="n">
+        <v>0.000203</v>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Legal and accounting fees</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr"/>
+      <c r="E369" s="5" t="n">
+        <v>0.001978</v>
+      </c>
+      <c r="F369" s="5" t="n">
+        <v>0.04149</v>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Stock-based compensation                                           77,855              −</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>INCOME (LOSS) BEFORE OTHER ITEM</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" s="5" t="n">
+        <v>-0.002069</v>
+      </c>
+      <c r="F370" s="5" t="n">
+        <v>-0.119548</v>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>NET AND COMPREHENSIVE INCOME (LOSS)</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>FOR THE PERIOD</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr"/>
+      <c r="E371" s="5" t="n">
+        <v>-0.002069</v>
+      </c>
+      <c r="F371" s="5" t="n">
+        <v>-0.116841</v>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>RETAINED EARNINGS (DEFICIT), beginning of period                        (2,069)             −</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>RETAINED EARNINGS (DEFICIT), end of period $</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr"/>
+      <c r="E372" s="5" t="n">
+        <v>-0.002069</v>
+      </c>
+      <c r="F372" s="5" t="n">
+        <v>-0.11891</v>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>NET INCOME (LOSS) PER SHARE,</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E373" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="F373" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>WEIGHTED AVERAGE NUMBER OF COMMON</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>SHARES OUTSTANDING</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E374" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F374" s="5" t="n">
+        <v>3.387075</v>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R374" t="inlineStr">
         <is>
           <t>-</t>
         </is>
